--- a/tests/BrandnameMT test/Brandnamedata.xlsx
+++ b/tests/BrandnameMT test/Brandnamedata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sarvam API\tests\BrandnameMT test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72101AAE-AF44-4D47-87F0-F8CDBA907B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196E63C0-9921-4844-87AB-DBFDFB5EBF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t xml:space="preserve">Sno </t>
   </si>
@@ -62,22 +62,97 @@
 Citroen C3 Feel Monotone</t>
   </si>
   <si>
-    <t>Citroen C4</t>
-  </si>
-  <si>
-    <t>Citroen C5</t>
-  </si>
-  <si>
-    <t>Citroen C6</t>
-  </si>
-  <si>
-    <t>Citroen C7</t>
-  </si>
-  <si>
-    <t>Citroen C8</t>
-  </si>
-  <si>
-    <t>Citroen C9</t>
+    <t>NotContains</t>
+  </si>
+  <si>
+    <t>“Hello,” she said, ‘the code’s formatting is completely broken.’</t>
+  </si>
+  <si>
+    <t>“,” ,‘,’,’s</t>
+  </si>
+  <si>
+    <t>The value of −5 × 4 ÷ 2 ≠ −10 according to the equation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≠ </t>
+  </si>
+  <si>
+    <t>The coefﬁcient dropped by ½ after a ﬆartling discovery in the ofﬁce.</t>
+  </si>
+  <si>
+    <t>½</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CEO of L'Oréal met the team at the café on Avenue des Champs-Élysées. </t>
+  </si>
+  <si>
+    <t>L'Oréal,Élysées</t>
+  </si>
+  <si>
+    <t xml:space="preserve">लाभों </t>
+  </si>
+  <si>
+    <t>ﬁT</t>
+  </si>
+  <si>
+    <t>Get the benefit amount to the extent of the value of beneﬁts</t>
+  </si>
+  <si>
+    <t>In comparing the Nothing Ear (&lt;n1&gt;) with the Nothing Ear (&lt;n2&gt;) earbuds, both models offer outstanding audio quality and cutting-edge features in Nothing's signature transparent design</t>
+  </si>
+  <si>
+    <t>(&lt;n1&gt;),(&lt;n2&gt;)</t>
+  </si>
+  <si>
+    <t>Initially, the Black-Scholes options pricing model did not factor in the impact of dividends paid during the option ‘s lifetime.</t>
+  </si>
+  <si>
+    <t>‘,‘s</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;Locate FASTag:&lt;/b&gt; Tap on 'FASTag'/’Buy FASTag’ under the 'BAJAJ PAY' section.</t>
+  </si>
+  <si>
+    <t>FASTag</t>
+  </si>
+  <si>
+    <t>he area is 55m² and it takes ½ hour.</t>
+  </si>
+  <si>
+    <t>55m²,½</t>
+  </si>
+  <si>
+    <t>The symbol for square yard is "yd²".</t>
+  </si>
+  <si>
+    <t>yd²</t>
+  </si>
+  <si>
+    <t>2½, 1¾, ¾</t>
+  </si>
+  <si>
+    <t>However, the model is often customised to consider dividends by computing the underlying asset’s ex-dividend date value.</t>
+  </si>
+  <si>
+    <t>’s,’</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make ### payments of ₹### or more across different recharge or bill categories </t>
+  </si>
+  <si>
+    <t>###,₹###</t>
+  </si>
+  <si>
+    <t>Vi Business #ReadyForNext MSME Growth Insights Study 2023:</t>
+  </si>
+  <si>
+    <t>#ReadyForNext</t>
+  </si>
+  <si>
+    <t>(ckycrr) for kyc verification</t>
+  </si>
+  <si>
+    <t>(ckycrr)</t>
   </si>
 </sst>
 </file>
@@ -450,14 +525,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="29.453125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+    <col min="5" max="5" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,8 +547,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -482,7 +562,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -493,7 +573,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -504,7 +584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -512,10 +592,10 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -523,10 +603,10 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -534,10 +614,10 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="58" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -545,10 +625,10 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -556,10 +636,10 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -567,7 +647,175 @@
         <v>11</v>
       </c>
       <c r="D10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/tests/BrandnameMT test/Brandnamedata.xlsx
+++ b/tests/BrandnameMT test/Brandnamedata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sarvam API\tests\BrandnameMT test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196E63C0-9921-4844-87AB-DBFDFB5EBF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBBCD34-221B-4D83-A420-CEF4D25E12AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -661,7 +661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
